--- a/成绩单模板.xlsx
+++ b/成绩单模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="成绩单模板" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>X年X班</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>姓名</t>
   </si>
@@ -1233,68 +1230,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1">
+        <v>2023001</v>
+      </c>
+      <c r="C2" s="1">
+        <v>98</v>
+      </c>
+      <c r="D2" s="1">
+        <v>95</v>
+      </c>
+      <c r="E2" s="1">
+        <v>90</v>
+      </c>
+      <c r="F2" s="1">
+        <v>92</v>
+      </c>
+      <c r="G2" s="1">
+        <v>375</v>
+      </c>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="1">
-        <v>2023001</v>
+        <v>2023002</v>
       </c>
       <c r="C3" s="1">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D3" s="1">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" s="1">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G3" s="1">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="H3" s="1"/>
     </row>
@@ -1303,53 +1312,26 @@
         <v>10</v>
       </c>
       <c r="B4" s="1">
-        <v>2023002</v>
+        <v>2023003</v>
       </c>
       <c r="C4" s="1">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D4" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F4" s="1">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G4" s="1">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2023003</v>
-      </c>
-      <c r="C5" s="1">
-        <v>92</v>
-      </c>
-      <c r="D5" s="1">
-        <v>90</v>
-      </c>
-      <c r="E5" s="1">
-        <v>93</v>
-      </c>
-      <c r="F5" s="1">
-        <v>94</v>
-      </c>
-      <c r="G5" s="1">
-        <v>369</v>
-      </c>
-      <c r="H5" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
